--- a/data_generation/06_soil_sorption/EFSA_means_soil_sorption.xlsx
+++ b/data_generation/06_soil_sorption/EFSA_means_soil_sorption.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Data-Work\41_AssessmentPPP-RE\412.34_Projekte\054_derappp\05_Daten\Input\06_soil_sorption\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6C8239-7AE5-46EB-A59B-4B7E8B820A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5210219F-64FE-4814-8A34-5DE0116B879C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="5710" windowWidth="19380" windowHeight="5620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="49">
   <si>
     <t>soil_type</t>
   </si>
@@ -123,9 +123,6 @@
     <t>luel</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
     <t>topsoil</t>
   </si>
   <si>
@@ -148,6 +145,42 @@
   </si>
   <si>
     <t>one_over_n</t>
+  </si>
+  <si>
+    <t>Triclopyr-butotyl</t>
+  </si>
+  <si>
+    <t>j.efsa.2024.8177_LoEP</t>
+  </si>
+  <si>
+    <t>Triclopyr</t>
+  </si>
+  <si>
+    <t>geometric</t>
+  </si>
+  <si>
+    <t>and p 45</t>
+  </si>
+  <si>
+    <t>Fluroxypyr</t>
+  </si>
+  <si>
+    <t>j.efsa.2011.2091</t>
+  </si>
+  <si>
+    <t>MCPB</t>
+  </si>
+  <si>
+    <t>Rewiev Report LoEP</t>
+  </si>
+  <si>
+    <t>Fluroxypyr-meptyl</t>
+  </si>
+  <si>
+    <t>MCPB-sodium</t>
+  </si>
+  <si>
+    <t>MCPB_RR_2005</t>
   </si>
 </sst>
 </file>
@@ -540,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.26953125" customWidth="1"/>
@@ -597,7 +630,7 @@
         <v>22</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>25</v>
@@ -643,11 +676,8 @@
       <c r="Q2">
         <v>8</v>
       </c>
-      <c r="R2" t="s">
-        <v>29</v>
-      </c>
       <c r="S2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="T2">
         <v>64</v>
@@ -659,7 +689,7 @@
         <v>7</v>
       </c>
       <c r="W2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X2" t="s">
         <v>28</v>
@@ -667,7 +697,7 @@
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3"/>
       <c r="C3"/>
@@ -688,11 +718,8 @@
       <c r="Q3">
         <v>7</v>
       </c>
-      <c r="R3" t="s">
-        <v>29</v>
-      </c>
       <c r="S3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T3">
         <v>56</v>
@@ -709,7 +736,7 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L4">
         <v>10000</v>
@@ -717,9 +744,6 @@
       <c r="P4" t="s">
         <v>8</v>
       </c>
-      <c r="R4" t="s">
-        <v>29</v>
-      </c>
       <c r="S4" t="s">
         <v>27</v>
       </c>
@@ -727,12 +751,195 @@
         <v>8</v>
       </c>
       <c r="V4" t="s">
+        <v>34</v>
+      </c>
+      <c r="W4" t="s">
         <v>35</v>
       </c>
-      <c r="W4" t="s">
-        <v>36</v>
-      </c>
       <c r="X4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5">
+        <v>57.95</v>
+      </c>
+      <c r="P5" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q5">
+        <v>5</v>
+      </c>
+      <c r="R5" t="s">
+        <v>40</v>
+      </c>
+      <c r="S5" t="s">
+        <v>38</v>
+      </c>
+      <c r="T5">
+        <v>65</v>
+      </c>
+      <c r="U5" t="s">
+        <v>8</v>
+      </c>
+      <c r="V5" t="s">
+        <v>7</v>
+      </c>
+      <c r="W5" t="s">
+        <v>41</v>
+      </c>
+      <c r="X5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6">
+        <v>5024</v>
+      </c>
+      <c r="P6" t="s">
+        <v>8</v>
+      </c>
+      <c r="R6" t="s">
+        <v>40</v>
+      </c>
+      <c r="S6" t="s">
+        <v>38</v>
+      </c>
+      <c r="T6">
+        <v>63</v>
+      </c>
+      <c r="U6" t="s">
+        <v>8</v>
+      </c>
+      <c r="V6" t="s">
+        <v>7</v>
+      </c>
+      <c r="W6" t="s">
+        <v>41</v>
+      </c>
+      <c r="X6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7">
+        <v>19550</v>
+      </c>
+      <c r="P7" t="s">
+        <v>8</v>
+      </c>
+      <c r="S7" t="s">
+        <v>43</v>
+      </c>
+      <c r="T7">
+        <v>49</v>
+      </c>
+      <c r="U7" t="s">
+        <v>8</v>
+      </c>
+      <c r="V7" t="s">
+        <v>7</v>
+      </c>
+      <c r="X7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8">
+        <v>68</v>
+      </c>
+      <c r="P8" t="s">
+        <v>8</v>
+      </c>
+      <c r="S8" t="s">
+        <v>43</v>
+      </c>
+      <c r="T8">
+        <v>52</v>
+      </c>
+      <c r="U8" t="s">
+        <v>8</v>
+      </c>
+      <c r="V8" t="s">
+        <v>7</v>
+      </c>
+      <c r="X8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="L9">
+        <v>108</v>
+      </c>
+      <c r="O9">
+        <v>0.81899999999999995</v>
+      </c>
+      <c r="P9" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q9">
+        <v>2</v>
+      </c>
+      <c r="S9" t="s">
+        <v>48</v>
+      </c>
+      <c r="T9">
+        <v>9</v>
+      </c>
+      <c r="U9" t="s">
+        <v>8</v>
+      </c>
+      <c r="V9" t="s">
+        <v>45</v>
+      </c>
+      <c r="X9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="L10">
+        <v>108</v>
+      </c>
+      <c r="O10">
+        <v>0.81899999999999995</v>
+      </c>
+      <c r="P10" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q10">
+        <v>2</v>
+      </c>
+      <c r="S10" t="s">
+        <v>48</v>
+      </c>
+      <c r="T10">
+        <v>9</v>
+      </c>
+      <c r="U10" t="s">
+        <v>8</v>
+      </c>
+      <c r="V10" t="s">
+        <v>45</v>
+      </c>
+      <c r="X10" t="s">
         <v>28</v>
       </c>
     </row>
